--- a/data/bingo/2025_11/bingo.xlsx
+++ b/data/bingo/2025_11/bingo.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sales-dashboard\modelscope-full\data\bingo\2025_11\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9324"/>
+    <workbookView windowWidth="22188" windowHeight="9324"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -59210,7 +59215,7 @@
         <v>36</v>
       </c>
       <c r="R672" s="4">
-        <v>688</v>
+        <v>675</v>
       </c>
       <c r="T672" s="3" t="s">
         <v>37</v>
@@ -59281,7 +59286,7 @@
         <v>36</v>
       </c>
       <c r="R673" s="4">
-        <v>674</v>
+        <v>652</v>
       </c>
       <c r="T673" s="3" t="s">
         <v>38</v>
@@ -59352,7 +59357,7 @@
         <v>31</v>
       </c>
       <c r="R674" s="4">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="T674" s="3" t="s">
         <v>30</v>
@@ -59423,7 +59428,7 @@
         <v>31</v>
       </c>
       <c r="R675" s="4">
-        <v>1630</v>
+        <v>1611</v>
       </c>
       <c r="T675" s="3" t="s">
         <v>32</v>
@@ -59494,7 +59499,7 @@
         <v>31</v>
       </c>
       <c r="R676" s="4">
-        <v>1843</v>
+        <v>1833</v>
       </c>
       <c r="T676" s="3" t="s">
         <v>33</v>
@@ -59565,7 +59570,7 @@
         <v>31</v>
       </c>
       <c r="R677" s="4">
-        <v>1622</v>
+        <v>1618</v>
       </c>
       <c r="T677" s="3" t="s">
         <v>34</v>
@@ -59636,7 +59641,7 @@
         <v>31</v>
       </c>
       <c r="R678" s="4">
-        <v>776</v>
+        <v>687</v>
       </c>
       <c r="T678" s="3" t="s">
         <v>35</v>
@@ -59705,7 +59710,7 @@
         <v>36</v>
       </c>
       <c r="R679" s="4">
-        <v>824</v>
+        <v>764</v>
       </c>
       <c r="T679" s="3" t="s">
         <v>37</v>
@@ -59774,7 +59779,7 @@
         <v>36</v>
       </c>
       <c r="R680" s="4">
-        <v>1040</v>
+        <v>995</v>
       </c>
       <c r="T680" s="3" t="s">
         <v>38</v>
@@ -59843,7 +59848,7 @@
         <v>31</v>
       </c>
       <c r="R681" s="4">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="T681" s="3" t="s">
         <v>30</v>
@@ -59912,7 +59917,7 @@
         <v>31</v>
       </c>
       <c r="R682" s="4">
-        <v>994</v>
+        <v>972</v>
       </c>
       <c r="T682" s="3" t="s">
         <v>32</v>
@@ -59981,7 +59986,7 @@
         <v>31</v>
       </c>
       <c r="R683" s="4">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="T683" s="3" t="s">
         <v>33</v>
@@ -60050,7 +60055,7 @@
         <v>31</v>
       </c>
       <c r="R684" s="4">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="T684" s="3" t="s">
         <v>34</v>
@@ -60119,7 +60124,7 @@
         <v>31</v>
       </c>
       <c r="R685" s="4">
-        <v>682</v>
+        <v>655</v>
       </c>
       <c r="T685" s="3" t="s">
         <v>35</v>
@@ -60188,7 +60193,7 @@
         <v>36</v>
       </c>
       <c r="R686" s="4">
-        <v>627</v>
+        <v>607</v>
       </c>
       <c r="T686" s="3" t="s">
         <v>37</v>
@@ -60257,7 +60262,7 @@
         <v>36</v>
       </c>
       <c r="R687" s="4">
-        <v>639</v>
+        <v>618</v>
       </c>
       <c r="T687" s="3" t="s">
         <v>38</v>
@@ -60325,6 +60330,9 @@
       <c r="Q688" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="R688" s="4">
+        <v>614</v>
+      </c>
       <c r="T688" s="3" t="s">
         <v>30</v>
       </c>
@@ -60391,6 +60399,9 @@
       <c r="Q689" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="R689" s="4">
+        <v>571</v>
+      </c>
       <c r="T689" s="3" t="s">
         <v>32</v>
       </c>
@@ -60457,6 +60468,9 @@
       <c r="Q690" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="R690" s="4">
+        <v>523</v>
+      </c>
       <c r="T690" s="3" t="s">
         <v>33</v>
       </c>
@@ -60523,6 +60537,9 @@
       <c r="Q691" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="R691" s="4">
+        <v>490</v>
+      </c>
       <c r="T691" s="3" t="s">
         <v>34</v>
       </c>
@@ -60589,6 +60606,9 @@
       <c r="Q692" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="R692" s="4">
+        <v>517</v>
+      </c>
       <c r="T692" s="3" t="s">
         <v>35</v>
       </c>
@@ -60655,6 +60675,9 @@
       <c r="Q693" s="3" t="s">
         <v>36</v>
       </c>
+      <c r="R693" s="4">
+        <v>513</v>
+      </c>
       <c r="T693" s="3" t="s">
         <v>37</v>
       </c>
@@ -60721,6 +60744,9 @@
       <c r="Q694" s="3" t="s">
         <v>36</v>
       </c>
+      <c r="R694" s="4">
+        <v>664</v>
+      </c>
       <c r="T694" s="3" t="s">
         <v>38</v>
       </c>
@@ -60787,6 +60813,9 @@
       <c r="Q695" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="R695" s="4">
+        <v>571</v>
+      </c>
       <c r="T695" s="3" t="s">
         <v>30</v>
       </c>
@@ -60853,6 +60882,9 @@
       <c r="Q696" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="R696" s="4">
+        <v>487</v>
+      </c>
       <c r="T696" s="3" t="s">
         <v>32</v>
       </c>
@@ -60919,6 +60951,9 @@
       <c r="Q697" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="R697" s="4">
+        <v>483</v>
+      </c>
       <c r="T697" s="3" t="s">
         <v>33</v>
       </c>
@@ -60985,6 +61020,9 @@
       <c r="Q698" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="R698" s="4">
+        <v>489</v>
+      </c>
       <c r="T698" s="3" t="s">
         <v>34</v>
       </c>
@@ -61051,6 +61089,9 @@
       <c r="Q699" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="R699" s="4">
+        <v>432</v>
+      </c>
       <c r="T699" s="3" t="s">
         <v>35</v>
       </c>
@@ -61117,6 +61158,9 @@
       <c r="Q700" s="3" t="s">
         <v>36</v>
       </c>
+      <c r="R700" s="4">
+        <v>447</v>
+      </c>
       <c r="T700" s="3" t="s">
         <v>37</v>
       </c>
@@ -61182,6 +61226,9 @@
       <c r="P701" s="3"/>
       <c r="Q701" s="3" t="s">
         <v>36</v>
+      </c>
+      <c r="R701" s="4">
+        <v>560</v>
       </c>
       <c r="T701" s="3" t="s">
         <v>38</v>
